--- a/panel_data.xlsx
+++ b/panel_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Tec21\CD3001B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silva\Documents\8vo\Nearshoring_Panel_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B7919-AE8B-4832-BF3F-DB3984EA32CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DD8287-078C-41C2-8684-8E648795C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C5DE6196-794B-4FFB-9DE2-95631F340A1A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C5DE6196-794B-4FFB-9DE2-95631F340A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="panel_data" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="98">
   <si>
     <t>state</t>
   </si>
@@ -331,13 +331,7 @@
     <t>INPC</t>
   </si>
   <si>
-    <t>Source: SE and Banxico. Elaborated by David Saucedo De La Fuente</t>
-  </si>
-  <si>
     <t>Exports</t>
-  </si>
-  <si>
-    <t>Note: New FDI and Exports in Millions of US Dollars</t>
   </si>
 </sst>
 </file>
@@ -464,7 +458,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -781,7 +775,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0462D48C-7251-445D-801E-D42BF7033944}">
   <dimension ref="A1:AA545"/>
-  <sheetFormatPr defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -45963,7 +45957,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292DB595-0914-40F6-88D7-13CDB1C80C95}">
   <dimension ref="A1:F77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.21875" bestFit="1" customWidth="1"/>
@@ -45990,7 +45984,7 @@
         <v>96</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -47474,9 +47468,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="10" t="s">
-        <v>99</v>
-      </c>
+      <c r="A76" s="10"/>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -47484,9 +47476,7 @@
       <c r="F76" s="10"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
-        <v>97</v>
-      </c>
+      <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
@@ -47505,7 +47495,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9410B5C-F2EF-48EC-B990-F7229333FFE3}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
     <col min="2" max="2" width="68" bestFit="1" customWidth="1"/>

--- a/panel_data.xlsx
+++ b/panel_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Tec21\CD3001B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silva\Documents\8vo\Nearshoring_Panel_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B7919-AE8B-4832-BF3F-DB3984EA32CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4D9829-0249-47D6-9096-FF0CC617BC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C5DE6196-794B-4FFB-9DE2-95631F340A1A}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{C5DE6196-794B-4FFB-9DE2-95631F340A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="panel_data" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="98">
   <si>
     <t>state</t>
   </si>
@@ -331,13 +331,7 @@
     <t>INPC</t>
   </si>
   <si>
-    <t>Source: SE and Banxico. Elaborated by David Saucedo De La Fuente</t>
-  </si>
-  <si>
     <t>Exports</t>
-  </si>
-  <si>
-    <t>Note: New FDI and Exports in Millions of US Dollars</t>
   </si>
 </sst>
 </file>
@@ -410,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -437,12 +431,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -464,7 +452,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -781,7 +769,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0462D48C-7251-445D-801E-D42BF7033944}">
   <dimension ref="A1:AA545"/>
-  <sheetFormatPr defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -45962,8 +45950,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292DB595-0914-40F6-88D7-13CDB1C80C95}">
-  <dimension ref="A1:F77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.21875" bestFit="1" customWidth="1"/>
@@ -45990,7 +45978,7 @@
         <v>96</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -47473,31 +47461,7 @@
         <v>46756.021000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A77:F77"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -47505,7 +47469,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9410B5C-F2EF-48EC-B990-F7229333FFE3}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
     <col min="2" max="2" width="68" bestFit="1" customWidth="1"/>
@@ -47680,10 +47644,10 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="12"/>
+      <c r="B22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
